--- a/заявки.xlsx
+++ b/заявки.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -551,6 +551,198 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:17:53</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Стрижка</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>жмых</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+79991234567</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15 марта 14:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:37:43</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Стрижка</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>жмых</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+79991234567</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5 июля 10:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:50:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Стрижка</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ddd</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>77575785858585</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+79991234567 10:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:54:40</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Диагностика</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ааа</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1243627273</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6 16:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-23 19:06:49</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Окрашивание</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>hhh</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>82536755467</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5 июля 16:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-23 19:12:36</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Стрижка</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ппп</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+79991234567</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5 июля 16:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
